--- a/WebApi/wwwroot/uploads/reports/2.xlsx
+++ b/WebApi/wwwroot/uploads/reports/2.xlsx
@@ -20,7 +20,7 @@
     <x:t>Transaction Detail</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-01  →  2026-06-15</x:t>
+    <x:t>2026-06-01  →  2026-07-03</x:t>
   </x:si>
   <x:si>
     <x:t>Date</x:t>
@@ -41,13 +41,13 @@
     <x:t>Notes</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ssss</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shopping</x:t>
+    <x:t>2026-07-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>طلعة</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Food &amp; Dining</x:t>
   </x:si>
   <x:si>
     <x:t>Expense</x:t>
@@ -56,13 +56,34 @@
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>test test</x:t>
+    <x:t>2026-07-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>مصروف</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Entertainment</x:t>
   </x:si>
   <x:si>
     <x:t>Other Income</x:t>
   </x:si>
   <x:si>
     <x:t>Income</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>اضافي عن شهر 06/26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bonus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>راتب شهر 06/26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Salary</x:t>
   </x:si>
   <x:si>
     <x:t>Transaction Summary</x:t>
@@ -218,7 +239,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="11">
+  <x:cellStyleXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -240,6 +261,12 @@
     <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -253,7 +280,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -279,6 +306,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -593,7 +628,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F6"/>
+  <x:dimension ref="A1:F9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14.710625" style="0" customWidth="1"/>
@@ -648,7 +683,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E5" s="5">
-        <x:v>5.55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
         <x:v>12</x:v>
@@ -656,21 +691,81 @@
     </x:row>
     <x:row r="6" spans="1:6" ht="18" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E6" s="7">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:6" ht="18" customHeight="1">
+      <x:c r="A7" s="4" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="7">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F6" s="6" t="s">
+      <x:c r="B7" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E7" s="8">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:6" ht="18" customHeight="1">
+      <x:c r="A8" s="6" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="9">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:6" ht="18" customHeight="1">
+      <x:c r="A9" s="4" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="8">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -701,39 +796,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" ht="20" customHeight="1">
-      <x:c r="A3" s="8" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B3" s="9">
-        <x:v>2</x:v>
+      <x:c r="A3" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="11">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" ht="20" customHeight="1">
-      <x:c r="A4" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B4" s="10">
-        <x:v>103</x:v>
+      <x:c r="A4" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B4" s="12">
+        <x:v>1423</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3" ht="20" customHeight="1">
-      <x:c r="A5" s="8" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B5" s="10">
-        <x:v>5.55</x:v>
+      <x:c r="A5" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B5" s="12">
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3" ht="20" customHeight="1">
-      <x:c r="A6" s="8" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B6" s="10">
-        <x:v>54.275</x:v>
+      <x:c r="A6" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B6" s="12">
+        <x:v>323.2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
